--- a/data/trans_orig/IP07C15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C15-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51063</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68039</t>
+          <t>68570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92115</t>
+          <t>91468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36462</t>
+          <t>36118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52574</t>
+          <t>52566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>55216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94501</t>
+          <t>95153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118893</t>
+          <t>119121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>26043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>49594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55189</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76810</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>57797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78819</t>
+          <t>79090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>118567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147983</t>
+          <t>148234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>65376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86336</t>
+          <t>86368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62027</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83612</t>
+          <t>83493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133392</t>
+          <t>133621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162778</t>
+          <t>163363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44591</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>34441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52142</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65190</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88929</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95466</t>
+          <t>95168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121505</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193121</t>
+          <t>195371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230975</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107433</t>
+          <t>106943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122217</t>
+          <t>122525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148924</t>
+          <t>150091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237225</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274964</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75337</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2549,62 +2549,62 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6178</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5589</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>60947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80230</t>
+          <t>80914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>75458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120023</t>
+          <t>119523</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65894</t>
+          <t>65642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72632</t>
+          <t>72841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103303</t>
+          <t>104122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132389</t>
+          <t>132291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>38812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60790</t>
+          <t>59374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51504</t>
+          <t>51251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71486</t>
+          <t>72430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65463</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87165</t>
+          <t>86361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>121648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152473</t>
+          <t>152764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71755</t>
+          <t>72420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>55857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>77080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113874</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141602</t>
+          <t>144296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72751</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118201</t>
+          <t>117926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>146257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126032</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154576</t>
+          <t>155017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250190</t>
+          <t>251055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291622</t>
+          <t>290972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131432</t>
+          <t>131845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113221</t>
+          <t>112581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>142107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224819</t>
+          <t>224334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266603</t>
+          <t>263905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70896</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93029</t>
+          <t>92629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>124462</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74799</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78834</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118838</t>
+          <t>118352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147492</t>
+          <t>149043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75648</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98396</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>67314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89081</t>
+          <t>88511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146630</t>
+          <t>148802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178005</t>
+          <t>179944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38202</t>
+          <t>38357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44963</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67171</t>
+          <t>67620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5644,77 +5644,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9182</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10751</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4121</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1533</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8635</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5465</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2394</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11177</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63501</t>
+          <t>63416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67490</t>
+          <t>68483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95215</t>
+          <t>95991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124375</t>
+          <t>124427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85228</t>
+          <t>86392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>77433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100370</t>
+          <t>100017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146884</t>
+          <t>147428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177665</t>
+          <t>178684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64827</t>
+          <t>64548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103515</t>
+          <t>103850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133354</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108236</t>
+          <t>111280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223257</t>
+          <t>223750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265214</t>
+          <t>263444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145558</t>
+          <t>143869</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175350</t>
+          <t>174849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>148698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182542</t>
+          <t>179339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305288</t>
+          <t>302145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346157</t>
+          <t>346191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>49761</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>126684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7101,82 +7101,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5858</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>64643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88016</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25672</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>38819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48502</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60132</t>
+          <t>61311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84228</t>
+          <t>83481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102626</t>
+          <t>102060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96797</t>
+          <t>97779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154732</t>
+          <t>157126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>48040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75656</t>
+          <t>76615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>117980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185451</t>
+          <t>185584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55198</t>
+          <t>54291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,47 +8597,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7628</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7854</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>90425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114784</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153356</t>
+          <t>153859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167640</t>
+          <t>167157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232476</t>
+          <t>229081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93164</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152018</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83358</t>
+          <t>84163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>118129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186849</t>
+          <t>187706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267336</t>
+          <t>260105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>74204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
